--- a/public/routers/A0_Sistema_FV/A61_Conectado_a_red/FV07_pvgisampliadomulti.xlsx
+++ b/public/routers/A0_Sistema_FV/A61_Conectado_a_red/FV07_pvgisampliadomulti.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Instalaciones S.A.</t>
+          <t>Instalaciones S..</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,70 +762,75 @@
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
+          <t>FVcost</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
           <t>mpptCount</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>vOc</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>vMp</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>iSc</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>iMp</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>coefVoc</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>vMax</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>vMinMppt</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>vMaxMppt</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>iMaxInverter</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>iScMaxInverter</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>paneles</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>sombras</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>geojson</t>
         </is>
@@ -856,10 +861,10 @@
         <v>1780997168256</v>
       </c>
       <c r="F2" t="n">
-        <v>36.66619701548809</v>
+        <v>36.66622525312856</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.461577758241837</v>
+        <v>-4.461580440402032</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -896,11 +901,11 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
+        <v>333</v>
+      </c>
+      <c r="U2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -920,253 +925,30 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['-1,-3','-1,-2','-1,-1','-1,0','-1,1','0,-3','0,-2','0,-1','0,0','0,1']</t>
-        </is>
+      <c r="AE2" t="n">
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>['1,-2','1,-1','2,-1','3,-1']</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>[1,1,21,21,1,1,1,1,1,1,1,1,1,1,1,1]</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>{'type':'FeatureCollection','features':[{'type':'Feature','properties':{'area':'G3','block':'-1,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461620874969667,36.66620468579217],[-4.461608555904573,36.66620468579217],[-4.461608555904573,36.66622002640032],[-4.461620874969667,36.66622002640032],[-4.461620874969667,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461608555904573,36.66620468579217],[-4.461596236839479,36.66620468579217],[-4.461596236839479,36.66622002640032],[-4.461608555904573,36.66622002640032],[-4.461608555904573,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461596236839479,36.66620468579217],[-4.461583917774385,36.66620468579217],[-4.461583917774385,36.66622002640032],[-4.461596236839479,36.66622002640032],[-4.461596236839479,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461583917774385,36.66620468579217],[-4.46157159870929,36.66620468579217],[-4.46157159870929,36.66622002640032],[-4.461583917774385,36.66622002640032],[-4.461583917774385,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46157159870929,36.66620468579217],[-4.461559279644196,36.66620468579217],[-4.461559279644196,36.66622002640032],[-4.46157159870929,36.66622002640032],[-4.46157159870929,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461620874969667,36.66618934518401],[-4.461608555904573,36.66618934518401],[-4.461608555904573,36.66620468579217],[-4.461620874969667,36.66620468579217],[-4.461620874969667,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461608555904573,36.66618934518401],[-4.461596236839479,36.66618934518401],[-4.461596236839479,36.66620468579217],[-4.461608555904573,36.66620468579217],[-4.461608555904573,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461596236839479,36.66618934518401],[-4.461583917774385,36.66618934518401],[-4.461583917774385,36.66620468579217],[-4.461596236839479,36.66620468579217],[-4.461596236839479,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461583917774385,36.66618934518401],[-4.46157159870929,36.66618934518401],[-4.46157159870929,36.66620468579217],[-4.461583917774385,36.66620468579217],[-4.461583917774385,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46157159870929,36.66618934518401],[-4.461559279644196,36.66618934518401],[-4.461559279644196,36.66620468579217],[-4.46157159870929,36.66620468579217],[-4.46157159870929,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.46121023591994,36.666106716932475],[-4.461202881311809,36.66611464417448],[-4.4612176645495865,36.66612346877769],[-4.461225019157716,36.66611554153569],[-4.46121023591994,36.666106716932475]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461202881311809,36.66611464417448],[-4.46119552670368,36.66612257141649],[-4.461210309941457,36.66613139601969],[-4.4612176645495865,36.66612346877769],[-4.461202881311809,36.66611464417448]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46119552670368,36.66612257141649],[-4.461188172095549,36.66613049865849],[-4.461202955333326,36.6661393232617],[-4.461210309941457,36.66613139601969],[-4.46119552670368,36.66612257141649]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461188172095549,36.66613049865849],[-4.46118081748742,36.66613842590049],[-4.461195600725197,36.666147250503705],[-4.461202955333326,36.6661393232617],[-4.461188172095549,36.66613049865849]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46118081748742,36.66613842590049],[-4.461173462879289,36.6661463531425],[-4.461188246117066,36.66615517774571],[-4.461195600725197,36.666147250503705],[-4.46118081748742,36.66613842590049]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461195452682163,36.66609789232926],[-4.461188098074032,36.66610581957127],[-4.461202881311809,36.66611464417448],[-4.46121023591994,36.666106716932475],[-4.461195452682163,36.66609789232926]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461188098074032,36.66610581957127],[-4.461180743465903,36.666113746813274],[-4.46119552670368,36.66612257141649],[-4.461202881311809,36.66611464417448],[-4.461188098074032,36.66610581957127]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461180743465903,36.666113746813274],[-4.461173388857772,36.66612167405528],[-4.461188172095549,36.66613049865849],[-4.46119552670368,36.66612257141649],[-4.461180743465903,36.666113746813274]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461173388857772,36.66612167405528],[-4.461166034249643,36.666129601297285],[-4.46118081748742,36.66613842590049],[-4.461188172095549,36.66613049865849],[-4.461173388857772,36.66612167405528]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461166034249643,36.666129601297285],[-4.461158679641512,36.66613752853929],[-4.461173462879289,36.6661463531425],[-4.46118081748742,36.66613842590049],[-4.461166034249643,36.666129601297285]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461285904003186,36.666104245877484],[-4.461275765106627,36.666098633165966],[-4.461265298160928,36.66611079857],[-4.4612754370574885,36.66611641128153],[-4.461285904003186,36.666104245877484]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461275765106627,36.666098633165966],[-4.461265626210066,36.66609302045444],[-4.461255159264368,36.666105185858484],[-4.461265298160928,36.66611079857],[-4.461275765106627,36.666098633165966]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461265626210066,36.66609302045444],[-4.4612554873135055,36.66608740774292],[-4.461245020367808,36.66609957314696],[-4.461255159264368,36.666105185858484],[-4.461265626210066,36.66609302045444]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461326787638565,36.66610891860801],[-4.461316648742005,36.666103305896485],[-4.4613061817963064,36.66611547130053],[-4.461316320692867,36.666121084012055],[-4.461326787638565,36.66610891860801]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461316648742005,36.666103305896485],[-4.4613065098454445,36.666097693184966],[-4.461296042899747,36.66610985858901],[-4.4613061817963064,36.66611547130053],[-4.461316648742005,36.666103305896485]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.4613065098454445,36.666097693184966],[-4.461296370948884,36.66609208047344],[-4.461285904003186,36.666104245877484],[-4.461296042899747,36.66610985858901],[-4.4613065098454445,36.666097693184966]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461296370948884,36.66609208047344],[-4.461286232052324,36.66608646776192],[-4.461275765106627,36.666098633165966],[-4.461285904003186,36.666104245877484],[-4.461296370948884,36.66609208047344]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461286232052324,36.66608646776192],[-4.461276093155764,36.666080855050396],[-4.461265626210066,36.66609302045444],[-4.461275765106627,36.666098633165966],[-4.461286232052324,36.66608646776192]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461276093155764,36.666080855050396],[-4.461265954259204,36.66607524233888],[-4.4612554873135055,36.66608740774292],[-4.461265626210066,36.66609302045444],[-4.461276093155764,36.666080855050396]]]}}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FV</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Paneles</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>coplanar</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1780945446828</v>
-      </c>
-      <c r="F3" t="n">
-        <v>36.66613004997789</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-4.461177103172596</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-53.3438915840331</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>30</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>vertical</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
-        <v>500</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['-1,-3','-1,-2','-1,-1','-1,0','-1,1','0,-3','0,-2','0,-1','0,0','0,1']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[1,1,1,1,1,1,1,1,29,1,1,1,1,1,1,1]</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>{'type':'FeatureCollection','features':[{'type':'Feature','properties':{'area':'G3','block':'-1,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461620874969667,36.66620468579217],[-4.461608555904573,36.66620468579217],[-4.461608555904573,36.66622002640032],[-4.461620874969667,36.66622002640032],[-4.461620874969667,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461608555904573,36.66620468579217],[-4.461596236839479,36.66620468579217],[-4.461596236839479,36.66622002640032],[-4.461608555904573,36.66622002640032],[-4.461608555904573,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461596236839479,36.66620468579217],[-4.461583917774385,36.66620468579217],[-4.461583917774385,36.66622002640032],[-4.461596236839479,36.66622002640032],[-4.461596236839479,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461583917774385,36.66620468579217],[-4.46157159870929,36.66620468579217],[-4.46157159870929,36.66622002640032],[-4.461583917774385,36.66622002640032],[-4.461583917774385,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46157159870929,36.66620468579217],[-4.461559279644196,36.66620468579217],[-4.461559279644196,36.66622002640032],[-4.46157159870929,36.66622002640032],[-4.46157159870929,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461620874969667,36.66618934518401],[-4.461608555904573,36.66618934518401],[-4.461608555904573,36.66620468579217],[-4.461620874969667,36.66620468579217],[-4.461620874969667,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461608555904573,36.66618934518401],[-4.461596236839479,36.66618934518401],[-4.461596236839479,36.66620468579217],[-4.461608555904573,36.66620468579217],[-4.461608555904573,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461596236839479,36.66618934518401],[-4.461583917774385,36.66618934518401],[-4.461583917774385,36.66620468579217],[-4.461596236839479,36.66620468579217],[-4.461596236839479,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461583917774385,36.66618934518401],[-4.46157159870929,36.66618934518401],[-4.46157159870929,36.66620468579217],[-4.461583917774385,36.66620468579217],[-4.461583917774385,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46157159870929,36.66618934518401],[-4.461559279644196,36.66618934518401],[-4.461559279644196,36.66620468579217],[-4.46157159870929,36.66620468579217],[-4.46157159870929,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.46121023591994,36.666106716932475],[-4.461202881311809,36.66611464417448],[-4.4612176645495865,36.66612346877769],[-4.461225019157716,36.66611554153569],[-4.46121023591994,36.666106716932475]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461202881311809,36.66611464417448],[-4.46119552670368,36.66612257141649],[-4.461210309941457,36.66613139601969],[-4.4612176645495865,36.66612346877769],[-4.461202881311809,36.66611464417448]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46119552670368,36.66612257141649],[-4.461188172095549,36.66613049865849],[-4.461202955333326,36.6661393232617],[-4.461210309941457,36.66613139601969],[-4.46119552670368,36.66612257141649]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461188172095549,36.66613049865849],[-4.46118081748742,36.66613842590049],[-4.461195600725197,36.666147250503705],[-4.461202955333326,36.6661393232617],[-4.461188172095549,36.66613049865849]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46118081748742,36.66613842590049],[-4.461173462879289,36.6661463531425],[-4.461188246117066,36.66615517774571],[-4.461195600725197,36.666147250503705],[-4.46118081748742,36.66613842590049]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461195452682163,36.66609789232926],[-4.461188098074032,36.66610581957127],[-4.461202881311809,36.66611464417448],[-4.46121023591994,36.666106716932475],[-4.461195452682163,36.66609789232926]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461188098074032,36.66610581957127],[-4.461180743465903,36.666113746813274],[-4.46119552670368,36.66612257141649],[-4.461202881311809,36.66611464417448],[-4.461188098074032,36.66610581957127]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461180743465903,36.666113746813274],[-4.461173388857772,36.66612167405528],[-4.461188172095549,36.66613049865849],[-4.46119552670368,36.66612257141649],[-4.461180743465903,36.666113746813274]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461173388857772,36.66612167405528],[-4.461166034249643,36.666129601297285],[-4.46118081748742,36.66613842590049],[-4.461188172095549,36.66613049865849],[-4.461173388857772,36.66612167405528]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461166034249643,36.666129601297285],[-4.461158679641512,36.66613752853929],[-4.461173462879289,36.6661463531425],[-4.46118081748742,36.66613842590049],[-4.461166034249643,36.666129601297285]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461285904003186,36.666104245877484],[-4.461275765106627,36.666098633165966],[-4.461265298160928,36.66611079857],[-4.4612754370574885,36.66611641128153],[-4.461285904003186,36.666104245877484]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461275765106627,36.666098633165966],[-4.461265626210066,36.66609302045444],[-4.461255159264368,36.666105185858484],[-4.461265298160928,36.66611079857],[-4.461275765106627,36.666098633165966]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461265626210066,36.66609302045444],[-4.4612554873135055,36.66608740774292],[-4.461245020367808,36.66609957314696],[-4.461255159264368,36.666105185858484],[-4.461265626210066,36.66609302045444]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461326787638565,36.66610891860801],[-4.461316648742005,36.666103305896485],[-4.4613061817963064,36.66611547130053],[-4.461316320692867,36.666121084012055],[-4.461326787638565,36.66610891860801]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461316648742005,36.666103305896485],[-4.4613065098454445,36.666097693184966],[-4.461296042899747,36.66610985858901],[-4.4613061817963064,36.66611547130053],[-4.461316648742005,36.666103305896485]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.4613065098454445,36.666097693184966],[-4.461296370948884,36.66609208047344],[-4.461285904003186,36.666104245877484],[-4.461296042899747,36.66610985858901],[-4.4613065098454445,36.666097693184966]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461296370948884,36.66609208047344],[-4.461286232052324,36.66608646776192],[-4.461275765106627,36.666098633165966],[-4.461285904003186,36.666104245877484],[-4.461296370948884,36.66609208047344]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461286232052324,36.66608646776192],[-4.461276093155764,36.666080855050396],[-4.461265626210066,36.66609302045444],[-4.461275765106627,36.666098633165966],[-4.461286232052324,36.66608646776192]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461276093155764,36.666080855050396],[-4.461265954259204,36.66607524233888],[-4.4612554873135055,36.66608740774292],[-4.461265626210066,36.66609302045444],[-4.461276093155764,36.666080855050396]]]}}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FV</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Paneles</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>coplanar</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1780945403876</v>
-      </c>
-      <c r="F4" t="n">
-        <v>36.6660953568197</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-4.461286068027755</v>
-      </c>
-      <c r="H4" t="n">
-        <v>34.61114218453039</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>30</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vertical</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>500</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['-1,0','-1,1','-1,2','0,-3','0,-2','0,-1','0,0','0,1','0,2']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[1,1,1,1,17,1,1,1,1,1,1,1,1,1,1,1]</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>{'type':'FeatureCollection','features':[{'type':'Feature','properties':{'area':'G3','block':'-1,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461620874969667,36.66620468579217],[-4.461608555904573,36.66620468579217],[-4.461608555904573,36.66622002640032],[-4.461620874969667,36.66622002640032],[-4.461620874969667,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461608555904573,36.66620468579217],[-4.461596236839479,36.66620468579217],[-4.461596236839479,36.66622002640032],[-4.461608555904573,36.66622002640032],[-4.461608555904573,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461596236839479,36.66620468579217],[-4.461583917774385,36.66620468579217],[-4.461583917774385,36.66622002640032],[-4.461596236839479,36.66622002640032],[-4.461596236839479,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461583917774385,36.66620468579217],[-4.46157159870929,36.66620468579217],[-4.46157159870929,36.66622002640032],[-4.461583917774385,36.66622002640032],[-4.461583917774385,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46157159870929,36.66620468579217],[-4.461559279644196,36.66620468579217],[-4.461559279644196,36.66622002640032],[-4.46157159870929,36.66622002640032],[-4.46157159870929,36.66620468579217]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461620874969667,36.66618934518401],[-4.461608555904573,36.66618934518401],[-4.461608555904573,36.66620468579217],[-4.461620874969667,36.66620468579217],[-4.461620874969667,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461608555904573,36.66618934518401],[-4.461596236839479,36.66618934518401],[-4.461596236839479,36.66620468579217],[-4.461608555904573,36.66620468579217],[-4.461608555904573,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461596236839479,36.66618934518401],[-4.461583917774385,36.66618934518401],[-4.461583917774385,36.66620468579217],[-4.461596236839479,36.66620468579217],[-4.461596236839479,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461583917774385,36.66618934518401],[-4.46157159870929,36.66618934518401],[-4.46157159870929,36.66620468579217],[-4.461583917774385,36.66620468579217],[-4.461583917774385,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G3','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46157159870929,36.66618934518401],[-4.461559279644196,36.66618934518401],[-4.461559279644196,36.66620468579217],[-4.46157159870929,36.66620468579217],[-4.46157159870929,36.66618934518401]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.46121023591994,36.666106716932475],[-4.461202881311809,36.66611464417448],[-4.4612176645495865,36.66612346877769],[-4.461225019157716,36.66611554153569],[-4.46121023591994,36.666106716932475]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461202881311809,36.66611464417448],[-4.46119552670368,36.66612257141649],[-4.461210309941457,36.66613139601969],[-4.4612176645495865,36.66612346877769],[-4.461202881311809,36.66611464417448]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46119552670368,36.66612257141649],[-4.461188172095549,36.66613049865849],[-4.461202955333326,36.6661393232617],[-4.461210309941457,36.66613139601969],[-4.46119552670368,36.66612257141649]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461188172095549,36.66613049865849],[-4.46118081748742,36.66613842590049],[-4.461195600725197,36.666147250503705],[-4.461202955333326,36.6661393232617],[-4.461188172095549,36.66613049865849]]]}},{'type':'Feature','properties':{'area':'G2','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.46118081748742,36.66613842590049],[-4.461173462879289,36.6661463531425],[-4.461188246117066,36.66615517774571],[-4.461195600725197,36.666147250503705],[-4.46118081748742,36.66613842590049]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461195452682163,36.66609789232926],[-4.461188098074032,36.66610581957127],[-4.461202881311809,36.66611464417448],[-4.46121023591994,36.666106716932475],[-4.461195452682163,36.66609789232926]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461188098074032,36.66610581957127],[-4.461180743465903,36.666113746813274],[-4.46119552670368,36.66612257141649],[-4.461202881311809,36.66611464417448],[-4.461188098074032,36.66610581957127]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461180743465903,36.666113746813274],[-4.461173388857772,36.66612167405528],[-4.461188172095549,36.66613049865849],[-4.46119552670368,36.66612257141649],[-4.461180743465903,36.666113746813274]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461173388857772,36.66612167405528],[-4.461166034249643,36.666129601297285],[-4.46118081748742,36.66613842590049],[-4.461188172095549,36.66613049865849],[-4.461173388857772,36.66612167405528]]]}},{'type':'Feature','properties':{'area':'G2','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461166034249643,36.666129601297285],[-4.461158679641512,36.66613752853929],[-4.461173462879289,36.6661463531425],[-4.46118081748742,36.66613842590049],[-4.461166034249643,36.666129601297285]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461285904003186,36.666104245877484],[-4.461275765106627,36.666098633165966],[-4.461265298160928,36.66611079857],[-4.4612754370574885,36.66611641128153],[-4.461285904003186,36.666104245877484]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461275765106627,36.666098633165966],[-4.461265626210066,36.66609302045444],[-4.461255159264368,36.666105185858484],[-4.461265298160928,36.66611079857],[-4.461275765106627,36.666098633165966]]]}},{'type':'Feature','properties':{'area':'G1','block':'-1,2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461265626210066,36.66609302045444],[-4.4612554873135055,36.66608740774292],[-4.461245020367808,36.66609957314696],[-4.461255159264368,36.666105185858484],[-4.461265626210066,36.66609302045444]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-3'},'geometry':{'type':'Polygon','coordinates':[[[-4.461326787638565,36.66610891860801],[-4.461316648742005,36.666103305896485],[-4.4613061817963064,36.66611547130053],[-4.461316320692867,36.666121084012055],[-4.461326787638565,36.66610891860801]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461316648742005,36.666103305896485],[-4.4613065098454445,36.666097693184966],[-4.461296042899747,36.66610985858901],[-4.4613061817963064,36.66611547130053],[-4.461316648742005,36.666103305896485]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.4613065098454445,36.666097693184966],[-4.461296370948884,36.66609208047344],[-4.461285904003186,36.666104245877484],[-4.461296042899747,36.66610985858901],[-4.4613065098454445,36.666097693184966]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,0'},'geometry':{'type':'Polygon','coordinates':[[[-4.461296370948884,36.66609208047344],[-4.461286232052324,36.66608646776192],[-4.461275765106627,36.666098633165966],[-4.461285904003186,36.666104245877484],[-4.461296370948884,36.66609208047344]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461286232052324,36.66608646776192],[-4.461276093155764,36.666080855050396],[-4.461265626210066,36.66609302045444],[-4.461275765106627,36.666098633165966],[-4.461286232052324,36.66608646776192]]]}},{'type':'Feature','properties':{'area':'G1','block':'0,2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461276093155764,36.666080855050396],[-4.461265954259204,36.66607524233888],[-4.4612554873135055,36.66608740774292],[-4.461265626210066,36.66609302045444],[-4.461276093155764,36.666080855050396]]]}}]}</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>{'type':'FeatureCollection','features':[{'type':'Feature','properties':{'area':'G3','block':'1,-2'},'geometry':{'type':'Polygon','coordinates':[[[-4.461611238076068,36.66620224221633],[-4.461598919006454,36.66620224221633],[-4.461598919006454,36.66621758282448],[-4.461611238076068,36.66621758282448],[-4.461611238076068,36.66620224221633]]]}},{'type':'Feature','properties':{'area':'G3','block':'1,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461598919006454,36.66620224221633],[-4.461586599936839,36.66620224221633],[-4.461586599936839,36.66621758282448],[-4.461598919006454,36.66621758282448],[-4.461598919006454,36.66620224221633]]]}},{'type':'Feature','properties':{'area':'G3','block':'2,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461598919006454,36.66618690160818],[-4.461586599936839,36.66618690160818],[-4.461586599936839,36.66620224221633],[-4.461598919006454,36.66620224221633],[-4.461598919006454,36.66618690160818]]]}},{'type':'Feature','properties':{'area':'G3','block':'3,-1'},'geometry':{'type':'Polygon','coordinates':[[[-4.461598919006454,36.66617156100003],[-4.461586599936839,36.66617156100003],[-4.461586599936839,36.66618690160818],[-4.461598919006454,36.66618690160818],[-4.461598919006454,36.66617156100003]]]}}]}</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1610,17 +1392,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Directo</t>
+          <t>Coste Directo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Equipos</t>
+          <t>Equipos Principales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Paneles FV (Monocristalinos)</t>
+          <t>Paneles fotovoltaicos monocristalinos</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1630,23 +1412,23 @@
         <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Directo</t>
+          <t>Coste Directo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equipos</t>
+          <t>Equipos Principales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inversor (String/Híbrido)</t>
+          <t>Inversor string/híbrido</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1656,56 +1438,56 @@
         <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Directo</t>
+          <t>Coste Directo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipos</t>
+          <t>Equipos Principales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sistema Baterías (Opcional)</t>
+          <t>Sistema de almacenamiento (Batería)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="E4" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Directo</t>
+          <t>Coste Directo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>Balance de Sistema (BOS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estructura soporte (Aluminio/Acero)</t>
+          <t>Soportes, cableado y protecciones</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>750</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
@@ -1714,76 +1496,76 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Directo</t>
+          <t>Coste Directo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>Balance de Sistema (BOS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cableado solar y protecciones (AC/DC)</t>
+          <t>Sistema de monitorización</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Directo</t>
+          <t>Coste Directo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Logística</t>
+          <t>Obra Civil</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Transporte y medios auxiliares</t>
+          <t>Adecuación y pequeñas adaptaciones</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Directo</t>
+          <t>Coste Indirecto</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Seguridad</t>
+          <t>Ingeniería</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seguridad en altura / EPIs</t>
+          <t>Proyecto, dirección y legalización</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F8" t="n">
         <v>100</v>
@@ -1792,156 +1574,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Directo</t>
+          <t>Coste Indirecto</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Obra Civil</t>
+          <t>Interconexión</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Adecuación y adaptaciones</t>
+          <t>Trámites con distribuidora y tasas</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Indirecto</t>
+          <t>Coste Indirecto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ingeniería</t>
+          <t>Gastos Generales</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Proyecto técnico y legalización</t>
+          <t>Margen comercial y overhead</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="F10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indirecto</t>
+          <t>Coste Indirecto</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gestión</t>
+          <t>Contingencias</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trámites, tasas e industria</t>
+          <t>Reserva para imprevistos (3-5%)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Indirecto</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Otros</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Margen comercial y Overhead</t>
+          <t>~</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Indirecto</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Riesgos</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Reserva imprevistos (5% sobre directos)</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>~</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
         <v>0</v>
       </c>
     </row>

--- a/public/routers/A0_Sistema_FV/A61_Conectado_a_red/FV07_pvgisampliadomulti.xlsx
+++ b/public/routers/A0_Sistema_FV/A61_Conectado_a_red/FV07_pvgisampliadomulti.xlsx
@@ -901,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>333</v>
+        <v>999</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
